--- a/data/supervision_pre_es.xlsx
+++ b/data/supervision_pre_es.xlsx
@@ -1,43 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="supervision" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="supervision" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
-  <si>
-    <t xml:space="preserve">what</t>
-  </si>
-  <si>
-    <t xml:space="preserve">when</t>
-  </si>
-  <si>
-    <t xml:space="preserve">with</t>
-  </si>
-  <si>
-    <t xml:space="preserve">where</t>
-  </si>
-  <si>
-    <t xml:space="preserve">why</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Psicología</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+  <si>
+    <t>what</t>
+  </si>
+  <si>
+    <t>when</t>
+  </si>
+  <si>
+    <t>with</t>
+  </si>
+  <si>
+    <t>where</t>
+  </si>
+  <si>
+    <t>why</t>
+  </si>
+  <si>
+    <t>Psicología</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 – 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana Sofía Reyes Torres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\href{https://www.unbosque.edu.co/}{Universidad El Bosque}, Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trabajo de grado:  \textit{\href{https://hdl.handle.net/20.500.12495/19678}{Atractivo facial y sociosexualidad como predictores de infidelidad: diferencias según el sexo}}</t>
   </si>
   <si>
     <t xml:space="preserve">2024 – 2025</t>
@@ -46,9 +54,6 @@
     <t xml:space="preserve">Juliana Pinzón Rodríguez y Valeria García Martínez</t>
   </si>
   <si>
-    <t xml:space="preserve">\href{https://www.unbosque.edu.co/}{Universidad El Bosque}, Colombia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trabajo de grado:  \textit{\href{https://hdl.handle.net/20.500.12495/18118}{¿Cómo influyen los rasgos faciales y las descripciones personales en la percepción de la sociosexualidad y la elección de pareja?}}</t>
   </si>
   <si>
@@ -79,7 +84,7 @@
     <t xml:space="preserve">2023 - 2024</t>
   </si>
   <si>
-    <t xml:space="preserve">Tifany Lexandra Mancera  Alméciga y  Jefferson Guillermo Suarez Zambrano</t>
+    <t xml:space="preserve">Tifany Lexandra Mancera Alméciga y  Jefferson Guillermo Suarez Zambrano</t>
   </si>
   <si>
     <t xml:space="preserve">Trabajo de grado:  \textit{\href{https://hdl.handle.net/20.500.12495/13144}{¿Somos capaces de detectar la tendencia a la infidelidad a partir de la voz?}}</t>
@@ -172,7 +177,7 @@
     <t xml:space="preserve">Trabajo de grado: \textit{Hombres que alcanzan voces menos agudas y con un volumen más bajo, tienden a tener más relaciones sexuales casuales}</t>
   </si>
   <si>
-    <t xml:space="preserve">Biología</t>
+    <t>Biología</t>
   </si>
   <si>
     <t xml:space="preserve">2017 - 2018</t>
@@ -238,32 +243,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -275,130 +266,388 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 2013 - 2022 Theme">
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -407,136 +656,182 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
                 <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultColWidth="58.57421875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="72.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="73.85"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" style="1" width="17.433571428571426"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" style="2" width="11.005000000000001"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" style="1" width="32.719285714285718"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" style="1" width="39.719285714285718"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" style="1" width="198.14785714285713"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -549,14 +844,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -566,31 +861,31 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -600,92 +895,92 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="E5" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6">
         <v>2023</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -695,14 +990,14 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -712,31 +1007,31 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>31</v>
       </c>
+      <c r="C13" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -746,14 +1041,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="18" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -763,14 +1058,14 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -780,99 +1075,99 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="3" t="s">
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="3" t="s">
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>54</v>
       </c>
+      <c r="C20" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>56</v>
+      <c r="B21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="B22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -882,31 +1177,31 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>61</v>
       </c>
+      <c r="C23" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="D23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="B24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>64</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -916,31 +1211,31 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>66</v>
       </c>
+      <c r="C25" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="D25" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="B26" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -950,101 +1245,104 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="3"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="Trabajo de grado:  \textit{\href{https://hdl.handle.net/20.500.12495/18118}{¿Cómo influyen los rasgos faciales y las descripciones personales en la percepción de la sociosexualidad y la elección de pareja?}}"/>
-    <hyperlink ref="E3" r:id="rId2" display="Trabajo de grado: \textit{\href{https://hdl.handle.net/20.500.12495/18119}{Sociosexualidad percibida a partir del contenido verbal de los discursos}}"/>
-    <hyperlink ref="E9" r:id="rId3" display="https://youtu.be/taKzODEX4zg"/>
-    <hyperlink ref="E10" r:id="rId4" display="https://youtu.be/RR7S5jRevsI"/>
-    <hyperlink ref="E11" r:id="rId5" display="https://youtu.be/NbPyhQAFlUk"/>
-    <hyperlink ref="E12" r:id="rId6" display="https://youtu.be/xhYq7HeEPP4"/>
-    <hyperlink ref="E13" r:id="rId7" display="https://youtu.be/5o9Iea8VfDM"/>
-    <hyperlink ref="E14" r:id="rId8" display="https://youtu.be/Ie07343LiIA"/>
-    <hyperlink ref="E16" r:id="rId9" display="https://youtu.be/rkp2k_KzZsM"/>
-  </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>